--- a/Datas/GameEventData.xlsx
+++ b/Datas/GameEventData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="GameEventData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -400,7 +400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
